--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846846</v>
+        <v>119846851</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475072</v>
+        <v>475052</v>
       </c>
       <c r="R3" t="n">
-        <v>6825241</v>
+        <v>6825192</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846851</v>
+        <v>119846846</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +903,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475052</v>
+        <v>475072</v>
       </c>
       <c r="R4" t="n">
-        <v>6825192</v>
+        <v>6825241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,6 +982,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846826</v>
+        <v>119846846</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475062</v>
+        <v>475072</v>
       </c>
       <c r="R2" t="n">
-        <v>6825247</v>
+        <v>6825241</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,17 +778,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846851</v>
+        <v>119846854</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -873,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846846</v>
+        <v>119846826</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,32 +903,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475072</v>
+        <v>475062</v>
       </c>
       <c r="R4" t="n">
-        <v>6825241</v>
+        <v>6825247</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846854</v>
+        <v>119846851</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,26 +1119,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846854</v>
+        <v>119846856</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475052</v>
+        <v>475065</v>
       </c>
       <c r="R3" t="n">
-        <v>6825192</v>
+        <v>6825184</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846856</v>
+        <v>119846854</v>
       </c>
       <c r="B5" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475065</v>
+        <v>475052</v>
       </c>
       <c r="R5" t="n">
-        <v>6825184</v>
+        <v>6825192</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846846</v>
+        <v>119846856</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475072</v>
+        <v>475065</v>
       </c>
       <c r="R2" t="n">
-        <v>6825241</v>
+        <v>6825184</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846856</v>
+        <v>119846851</v>
       </c>
       <c r="B3" t="n">
-        <v>78560</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475065</v>
+        <v>475052</v>
       </c>
       <c r="R3" t="n">
-        <v>6825184</v>
+        <v>6825192</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846826</v>
+        <v>119846846</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +903,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475062</v>
+        <v>475072</v>
       </c>
       <c r="R4" t="n">
-        <v>6825247</v>
+        <v>6825241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,17 +994,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846854</v>
+        <v>119846826</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475052</v>
+        <v>475062</v>
       </c>
       <c r="R5" t="n">
-        <v>6825192</v>
+        <v>6825247</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,17 +1100,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846851</v>
+        <v>119846854</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,31 +1123,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>119846839</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846856</v>
+        <v>119846826</v>
       </c>
       <c r="B2" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475065</v>
+        <v>475062</v>
       </c>
       <c r="R2" t="n">
-        <v>6825184</v>
+        <v>6825247</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846851</v>
+        <v>119846856</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475052</v>
+        <v>475065</v>
       </c>
       <c r="R3" t="n">
-        <v>6825192</v>
+        <v>6825184</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846846</v>
+        <v>119846851</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +899,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -938,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475072</v>
+        <v>475052</v>
       </c>
       <c r="R4" t="n">
-        <v>6825241</v>
+        <v>6825192</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846826</v>
+        <v>119846854</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475062</v>
+        <v>475052</v>
       </c>
       <c r="R5" t="n">
-        <v>6825247</v>
+        <v>6825192</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846854</v>
+        <v>119846846</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,28 +1115,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475052</v>
+        <v>475072</v>
       </c>
       <c r="R6" t="n">
-        <v>6825192</v>
+        <v>6825241</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846826</v>
+        <v>119846856</v>
       </c>
       <c r="B2" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475062</v>
+        <v>475065</v>
       </c>
       <c r="R2" t="n">
-        <v>6825247</v>
+        <v>6825184</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846856</v>
+        <v>119846846</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,28 +793,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475065</v>
+        <v>475072</v>
       </c>
       <c r="R3" t="n">
-        <v>6825184</v>
+        <v>6825241</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846851</v>
+        <v>119846854</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,31 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846854</v>
+        <v>119846826</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475052</v>
+        <v>475062</v>
       </c>
       <c r="R5" t="n">
-        <v>6825192</v>
+        <v>6825247</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846846</v>
+        <v>119846851</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475072</v>
+        <v>475052</v>
       </c>
       <c r="R6" t="n">
-        <v>6825241</v>
+        <v>6825192</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846856</v>
+        <v>119846851</v>
       </c>
       <c r="B2" t="n">
-        <v>78576</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475065</v>
+        <v>475052</v>
       </c>
       <c r="R2" t="n">
-        <v>6825184</v>
+        <v>6825192</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846846</v>
+        <v>119846854</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,32 +797,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475072</v>
+        <v>475052</v>
       </c>
       <c r="R3" t="n">
-        <v>6825241</v>
+        <v>6825192</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846854</v>
+        <v>119846826</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475052</v>
+        <v>475062</v>
       </c>
       <c r="R4" t="n">
-        <v>6825192</v>
+        <v>6825247</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,17 +990,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846826</v>
+        <v>119846846</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,28 +1009,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1040,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475062</v>
+        <v>475072</v>
       </c>
       <c r="R5" t="n">
-        <v>6825247</v>
+        <v>6825241</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,17 +1100,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846851</v>
+        <v>119846856</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,31 +1123,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475052</v>
+        <v>475065</v>
       </c>
       <c r="R6" t="n">
-        <v>6825192</v>
+        <v>6825184</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119846851</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34197-2023 artfynd.xlsx
+++ b/artfynd/A 34197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119846851</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
